--- a/data/trans_orig/P41E_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023</t>
+          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27410</t>
+          <t>27658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47866</t>
+          <t>47840</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26894</t>
+          <t>26242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44268</t>
+          <t>42046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57130</t>
+          <t>59251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83760</t>
+          <t>84349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35870</t>
+          <t>36633</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27673</t>
+          <t>28937</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52523</t>
+          <t>52837</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27955</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45699</t>
+          <t>45853</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61904</t>
+          <t>61625</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91216</t>
+          <t>92385</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79385</t>
+          <t>79441</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113716</t>
+          <t>112539</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91932</t>
+          <t>92514</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118413</t>
+          <t>119437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179409</t>
+          <t>178864</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>223324</t>
+          <t>222817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>141763</t>
+          <t>143448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>183120</t>
+          <t>182642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120754</t>
+          <t>121745</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149046</t>
+          <t>149051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>272669</t>
+          <t>271478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>323649</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42492</t>
+          <t>42456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26433</t>
+          <t>26256</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42879</t>
+          <t>42494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>30519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79445</t>
+          <t>82680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36656</t>
+          <t>35925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39048</t>
+          <t>38620</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68178</t>
+          <t>69981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>13994</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69991</t>
+          <t>68776</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33556</t>
+          <t>32402</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52591</t>
+          <t>52421</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37809</t>
+          <t>47577</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110775</t>
+          <t>113368</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51665</t>
+          <t>56800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>219438</t>
+          <t>214906</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117529</t>
+          <t>116807</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150587</t>
+          <t>149801</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131544</t>
+          <t>149502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>355522</t>
+          <t>354293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>395104</t>
+          <t>397777</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>663970</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>213112</t>
+          <t>214807</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248708</t>
+          <t>250009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>624202</t>
+          <t>620468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>997676</t>
+          <t>962924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>78,97%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14157</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20282</t>
+          <t>20520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7439</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>19300</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>36405</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49801</t>
+          <t>49262</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96487</t>
+          <t>96167</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>128366</t>
+          <t>128912</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31824</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>198090</t>
+          <t>198339</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90850</t>
+          <t>88330</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>318202</t>
+          <t>317719</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76512</t>
+          <t>76354</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>109863</t>
+          <t>108863</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186296</t>
+          <t>185799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>393736</t>
+          <t>385641</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>272427</t>
+          <t>270806</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>553344</t>
+          <t>554699</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29759</t>
+          <t>30431</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51396</t>
+          <t>51065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>39860</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59112</t>
+          <t>59368</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73426</t>
+          <t>73318</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>103150</t>
+          <t>104003</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>17414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34393</t>
+          <t>34826</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>22652</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32262</t>
+          <t>31864</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52228</t>
+          <t>51569</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46916</t>
+          <t>46629</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>72103</t>
+          <t>71321</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60440</t>
+          <t>61227</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84392</t>
+          <t>84693</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>111981</t>
+          <t>114859</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>147082</t>
+          <t>148781</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>101254</t>
+          <t>101782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>138019</t>
+          <t>138631</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87379</t>
+          <t>87888</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>117196</t>
+          <t>114970</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>196506</t>
+          <t>196442</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>242247</t>
+          <t>243756</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>170089</t>
+          <t>171653</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>210750</t>
+          <t>208913</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>185850</t>
+          <t>183393</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>220475</t>
+          <t>219524</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>367014</t>
+          <t>366438</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>422363</t>
+          <t>419181</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>64115</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132696</t>
+          <t>134859</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>82298</t>
+          <t>76296</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>146997</t>
+          <t>146786</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>176937</t>
+          <t>172926</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>269334</t>
+          <t>269810</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39620</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>84648</t>
+          <t>84869</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>40239</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>76549</t>
+          <t>76625</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>96351</t>
+          <t>93737</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>153837</t>
+          <t>152135</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>93251</t>
+          <t>95933</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>185680</t>
+          <t>189898</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107609</t>
+          <t>106968</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>199222</t>
+          <t>197019</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>239826</t>
+          <t>236783</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>369225</t>
+          <t>367288</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>291134</t>
+          <t>294676</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>559499</t>
+          <t>559933</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>295654</t>
+          <t>289168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>510895</t>
+          <t>511166</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>688219</t>
+          <t>678010</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1042641</t>
+          <t>1041990</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>822842</t>
+          <t>817951</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1261126</t>
+          <t>1251991</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>758941</t>
+          <t>754114</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1136916</t>
+          <t>1165183</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1612295</t>
+          <t>1606545</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2225227</t>
+          <t>2231183</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41E_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36556</t>
+          <t>37831</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27658</t>
+          <t>28336</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47840</t>
+          <t>50457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33684</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26242</t>
+          <t>27407</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42046</t>
+          <t>43740</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70241</t>
+          <t>73564</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59251</t>
+          <t>60880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84349</t>
+          <t>88593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19238</t>
+          <t>20816</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14077</t>
+          <t>15459</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19445</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26979</t>
+          <t>29050</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19463</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36633</t>
+          <t>38846</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39332</t>
+          <t>39250</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52837</t>
+          <t>52759</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36218</t>
+          <t>37840</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>29679</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45853</t>
+          <t>49260</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>75550</t>
+          <t>77090</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>63259</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92385</t>
+          <t>92647</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94736</t>
+          <t>104044</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79441</t>
+          <t>87087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112539</t>
+          <t>122037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>105240</t>
+          <t>112411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92514</t>
+          <t>98767</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119437</t>
+          <t>126419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>199976</t>
+          <t>216455</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178864</t>
+          <t>195616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>222817</t>
+          <t>242344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>163005</t>
+          <t>172896</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>143448</t>
+          <t>151487</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>182642</t>
+          <t>193232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>134837</t>
+          <t>143379</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121745</t>
+          <t>130144</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149051</t>
+          <t>158922</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>297842</t>
+          <t>316276</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>271478</t>
+          <t>288914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>323649</t>
+          <t>339491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>346532</t>
+          <t>367611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>346532</t>
+          <t>367611</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>346532</t>
+          <t>367611</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>324056</t>
+          <t>344822</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>324056</t>
+          <t>344822</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>324056</t>
+          <t>344822</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>670588</t>
+          <t>712434</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>670588</t>
+          <t>712434</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>670588</t>
+          <t>712434</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25769</t>
+          <t>28039</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42456</t>
+          <t>38623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33851</t>
+          <t>37117</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26256</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42494</t>
+          <t>46605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>59620</t>
+          <t>65156</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30519</t>
+          <t>53244</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82680</t>
+          <t>78983</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>23929</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>17009</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35925</t>
+          <t>34850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28844</t>
+          <t>32365</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38620</t>
+          <t>43975</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>50645</t>
+          <t>56294</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>45328</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69981</t>
+          <t>70693</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42288</t>
+          <t>49497</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13994</t>
+          <t>36845</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68776</t>
+          <t>65778</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41812</t>
+          <t>44715</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32402</t>
+          <t>34786</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52421</t>
+          <t>55021</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>84100</t>
+          <t>94212</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47577</t>
+          <t>76956</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>113368</t>
+          <t>111572</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>140615</t>
+          <t>158056</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56800</t>
+          <t>138405</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214906</t>
+          <t>181597</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>133380</t>
+          <t>151336</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116807</t>
+          <t>133946</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149801</t>
+          <t>169608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>273995</t>
+          <t>309392</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149502</t>
+          <t>281003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>354293</t>
+          <t>338146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>518915</t>
+          <t>300984</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>397777</t>
+          <t>273334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>658402</t>
+          <t>323914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>232050</t>
+          <t>251644</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214807</t>
+          <t>233210</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>250009</t>
+          <t>271403</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>750965</t>
+          <t>552628</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>620468</t>
+          <t>519139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>962924</t>
+          <t>582986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>749388</t>
+          <t>560505</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>749388</t>
+          <t>560505</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>749388</t>
+          <t>560505</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>469937</t>
+          <t>517178</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>469937</t>
+          <t>517178</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>469937</t>
+          <t>517178</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1219325</t>
+          <t>1077683</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1219325</t>
+          <t>1077683</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1219325</t>
+          <t>1077683</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10266</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>13637</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>20698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17499</t>
+          <t>16993</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>19877</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>31145</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17593</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36405</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>30042</t>
+          <t>39461</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11857</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49262</t>
+          <t>53230</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>112751</t>
+          <t>129975</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96167</t>
+          <t>112725</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>128912</t>
+          <t>147928</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>100411</t>
+          <t>120933</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>107942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>198339</t>
+          <t>135868</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>213163</t>
+          <t>250909</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88330</t>
+          <t>226499</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>317719</t>
+          <t>272731</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>92357</t>
+          <t>103604</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76354</t>
+          <t>86110</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108863</t>
+          <t>122310</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>307719</t>
+          <t>123068</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>185799</t>
+          <t>108892</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>385641</t>
+          <t>138616</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>400076</t>
+          <t>226672</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>270806</t>
+          <t>205261</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>554699</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>46,7%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>230552</t>
+          <t>267783</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>230552</t>
+          <t>267783</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>230552</t>
+          <t>267783</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>433818</t>
+          <t>273029</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>433818</t>
+          <t>273029</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>433818</t>
+          <t>273029</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>664370</t>
+          <t>540813</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>664370</t>
+          <t>540813</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>664370</t>
+          <t>540813</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>39399</t>
+          <t>41953</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30431</t>
+          <t>31722</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51065</t>
+          <t>53544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>48963</t>
+          <t>53672</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39860</t>
+          <t>43456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59368</t>
+          <t>65582</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>88362</t>
+          <t>95625</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73318</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104003</t>
+          <t>112063</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24949</t>
+          <t>26757</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>18509</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34826</t>
+          <t>36473</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>16848</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>11508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22652</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,27 +2954,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>40542</t>
+          <t>43605</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31864</t>
+          <t>33978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51569</t>
+          <t>55977</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>58359</t>
+          <t>59648</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46629</t>
+          <t>46985</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71321</t>
+          <t>73109</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>71881</t>
+          <t>78778</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61227</t>
+          <t>66837</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84693</t>
+          <t>93809</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>130240</t>
+          <t>138426</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114859</t>
+          <t>120087</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>148781</t>
+          <t>157192</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>119232</t>
+          <t>131951</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>101782</t>
+          <t>114096</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>138631</t>
+          <t>153566</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>100913</t>
+          <t>118100</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87888</t>
+          <t>102330</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114970</t>
+          <t>135688</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>220146</t>
+          <t>250051</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>196442</t>
+          <t>224540</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>243756</t>
+          <t>275634</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>190250</t>
+          <t>202731</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>171653</t>
+          <t>181485</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>208913</t>
+          <t>224941</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>202145</t>
+          <t>215550</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>183393</t>
+          <t>197496</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>219524</t>
+          <t>234065</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>392394</t>
+          <t>418281</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>366438</t>
+          <t>389226</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>419181</t>
+          <t>446137</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,16%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>432189</t>
+          <t>463039</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>432189</t>
+          <t>463039</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>432189</t>
+          <t>463039</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>439495</t>
+          <t>482948</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>439495</t>
+          <t>482948</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>439495</t>
+          <t>482948</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>871684</t>
+          <t>945987</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>871684</t>
+          <t>945987</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>871684</t>
+          <t>945987</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>107335</t>
+          <t>114086</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>66021</t>
+          <t>96482</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>134859</t>
+          <t>133023</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>122688</t>
+          <t>133895</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>76296</t>
+          <t>117722</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>146786</t>
+          <t>152309</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>230023</t>
+          <t>247981</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>172926</t>
+          <t>223971</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>269810</t>
+          <t>275122</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>67036</t>
+          <t>72339</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>58025</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>84869</t>
+          <t>86950</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>66744</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40239</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>76625</t>
+          <t>79844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>127455</t>
+          <t>139083</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>93737</t>
+          <t>121019</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>152135</t>
+          <t>161332</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>152429</t>
+          <t>168271</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>95933</t>
+          <t>143513</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>189898</t>
+          <t>189431</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>167503</t>
+          <t>180917</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>106968</t>
+          <t>159847</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>197019</t>
+          <t>201626</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>319932</t>
+          <t>349189</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>236783</t>
+          <t>317876</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>367288</t>
+          <t>381411</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>467334</t>
+          <t>524027</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>294676</t>
+          <t>485206</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>559933</t>
+          <t>563621</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>439945</t>
+          <t>502780</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>289168</t>
+          <t>471577</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>511166</t>
+          <t>532257</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>907279</t>
+          <t>1026807</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>678010</t>
+          <t>977498</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1041990</t>
+          <t>1079154</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>964527</t>
+          <t>780215</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>817951</t>
+          <t>737074</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1251991</t>
+          <t>821380</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>876751</t>
+          <t>733642</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>754114</t>
+          <t>697805</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1165183</t>
+          <t>767634</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1841278</t>
+          <t>1513856</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1606545</t>
+          <t>1460505</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2231183</t>
+          <t>1567867</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">

--- a/data/trans_orig/P41E_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
+          <t>Población según su nivel de acuerdo sobre la satisfacción de sus relaciones sexuales por ambas partes en el último mes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
